--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_element_info/lang_element_info__name_title__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_element_info/lang_element_info__name_title__part_0001.xlsx
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>test/Không description needed</t>
+          <t>test/No description needed</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Giai đoạn 2 Concerto</t>
+          <t>Phase 2 Concerto</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
